--- a/information_request_forms/010_sustainable_teaching_toolkit_request_form--information_request_forms.xlsx
+++ b/information_request_forms/010_sustainable_teaching_toolkit_request_form--information_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>What is the primary topic of your request?</t>
+          <t>Primary Topic of Request</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,13 +571,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>What is your preferred email format for communication?</t>
+          <t>Email Format Preference</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,13 +594,13 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What type of resource do you need?</t>
+          <t>Type of Resource Needed</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,13 +617,13 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What format would you prefer for these resources?</t>
+          <t>Resource Format Preference</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -640,20 +640,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Do you have any specific dates or deadlines for the resource?</t>
+          <t>Deadline or Specific Date</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,20 +663,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Do you have any specific dates or deadlines for the resource?</t>
+          <t>Request Description</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,24 +686,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Please specify a date or deadline</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Please enter a date or time in the format mm/dd/yyyy or 12:00 PM</t>
-        </is>
-      </c>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -713,13 +709,13 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Please describe your request</t>
+          <t>Institutional Affiliation</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -736,13 +732,13 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What is your name</t>
+          <t>Contact Method</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -759,20 +755,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What school do you represent</t>
+          <t>Follow-up Request</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -782,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>How will we get in touch with you?</t>
+          <t>Contact Method 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -795,7 +791,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -805,20 +801,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Is this a follow-up call or email?</t>
+          <t>Best Time of Day</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -828,264 +824,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>How can we get back to you?</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>form_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Do you have a preferred contact method</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>form_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Please provide a contact number</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>form_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Please provide a contact number</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>form_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Please provide a contact number</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>form_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Please provide a contact number</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>form_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Please provide a contact number</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>form_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Please provide a contact number</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>form_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>What is the best time of day to contact you</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>form_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Best time of day to contact you</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>form_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Additional comments</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>form_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Additional comments</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1102,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1130,748 +873,527 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>form_2_choices</t>
+          <t>form_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>math</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Math</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>form_2_choices</t>
+          <t>form_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>science</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Science</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>form_3_choices</t>
+          <t>form_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>html</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>form_3_choices</t>
+          <t>form_1_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>plain</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plain</t>
+          <t>History</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>form_3_choices</t>
+          <t>form_1_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>form_4_choices</t>
+          <t>form_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>lesson_plans</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lesson Plans</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>form_4_choices</t>
+          <t>form_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>videos</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Videos</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>form_4_choices</t>
+          <t>form_3_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>books</t>
+          <t>html</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Books</t>
+          <t>HTML</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>form_4_choices</t>
+          <t>form_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>weblinks</t>
+          <t>plain</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Weblinks</t>
+          <t>Plain</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>form_4_choices</t>
+          <t>form_3_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>form_5_choices</t>
+          <t>form_4_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>lesson_plans</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>Lesson Plans</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>form_5_choices</t>
+          <t>form_4_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ppt</t>
+          <t>videos</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PPT</t>
+          <t>Videos</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>form_5_choices</t>
+          <t>form_4_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>books</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DOCX</t>
+          <t>Books</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>form_5_choices</t>
+          <t>form_4_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>html</t>
+          <t>weblinks</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>Weblinks</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>form_8_choices</t>
+          <t>form_4_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>mm/dd/yyyy</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>mm/dd/yyyy</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>form_8_choices</t>
+          <t>form_5_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:00_pm</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>PDF</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>form_10_choices</t>
+          <t>form_5_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>mr.</t>
+          <t>ppt</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mr.</t>
+          <t>PPT</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>form_10_choices</t>
+          <t>form_5_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>mrs.</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Mrs.</t>
+          <t>DOCX</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>form_10_choices</t>
+          <t>form_5_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ms.</t>
+          <t>html</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ms.</t>
+          <t>HTML</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>form_10_choices</t>
+          <t>form_9_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>dr.</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dr.</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>form_10_choices</t>
+          <t>form_9_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>college/university</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>College/University</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>form_11_choices</t>
+          <t>form_9_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>high_school</t>
+          <t>community_college</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>High School</t>
+          <t>Community College</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>form_11_choices</t>
+          <t>form_9_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>college/university</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>College/University</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>form_11_choices</t>
+          <t>form_10_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>community_college</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Community College</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>form_11_choices</t>
+          <t>form_10_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>form_13_choices</t>
+          <t>form_10_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Text</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>form_13_choices</t>
+          <t>form_11_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>form_14_choices</t>
+          <t>form_11_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>form_14_choices</t>
+          <t>form_12_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>form_14_choices</t>
+          <t>form_12_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>form_15_choices</t>
+          <t>form_12_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Phone</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>form_15_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>form_15_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
           <t>Text</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>form_17_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>form_17_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>work</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Work</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>form_17_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>cell</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Cell</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>form_18_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>work</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Work</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>form_18_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>cell</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Cell</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>form_19_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>cell</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Cell</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>form_19_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>form_20_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>form_20_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>form_21_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>form_21_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Other</t>
         </is>
       </c>
     </row>
